--- a/Setor de Locação/Faixa de Diárias - Padrão, Feriados e Alta.xlsx
+++ b/Setor de Locação/Faixa de Diárias - Padrão, Feriados e Alta.xlsx
@@ -138,8 +138,8 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -530,7 +530,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fonte: calendário de preços da Stays, 03/10/2026 a 30/09/2027. Feriados e Alta temporada = datas da aba 'Calendário'; Tarifa Padrão = todas as demais datas.</t>
+          <t>Fonte: calendário de preços da Stays, 03/10/2026 a 30/09/2027. Datas de Feriados e Alta temporada conforme visite.portosegurobahia.com.br/tabela (aba 'Calendário'); Tarifa Padrão = todas as demais datas.</t>
         </is>
       </c>
     </row>
@@ -579,6 +579,18 @@
 Faixa</t>
         </is>
       </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Alta temporada
+Média</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Alta temporada
+Faixa</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -600,27 +612,27 @@
         <v>5</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>R$ 250 – R$ 600</t>
+          <t>R$ 250 – R$ 494</t>
         </is>
       </c>
       <c r="G5" s="8" t="n">
-        <v>449</v>
+        <v>415</v>
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>R$ 288 – R$ 650</t>
+          <t>R$ 380 – R$ 494</t>
         </is>
       </c>
       <c r="I5" s="10" t="n">
-        <v>795</v>
+        <v>613</v>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>R$ 500 – R$ 1.000</t>
+          <t>R$ 250 – R$ 1.000</t>
         </is>
       </c>
     </row>
@@ -644,7 +656,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
@@ -652,19 +664,19 @@
         </is>
       </c>
       <c r="G6" s="8" t="n">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>R$ 288 – R$ 510</t>
+          <t>R$ 380 – R$ 494</t>
         </is>
       </c>
       <c r="I6" s="10" t="n">
-        <v>702</v>
+        <v>584</v>
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>R$ 490 – R$ 1.100</t>
+          <t>R$ 250 – R$ 1.100</t>
         </is>
       </c>
     </row>
@@ -688,27 +700,27 @@
         <v>8</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>518</v>
+        <v>492</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>R$ 400 – R$ 1.050</t>
+          <t>R$ 400 – R$ 650</t>
         </is>
       </c>
       <c r="G7" s="8" t="n">
-        <v>787</v>
+        <v>733</v>
       </c>
       <c r="H7" s="9" t="inlineStr">
         <is>
-          <t>R$ 518 – R$ 1.300</t>
+          <t>R$ 600 – R$ 1.300</t>
         </is>
       </c>
       <c r="I7" s="10" t="n">
-        <v>1165</v>
+        <v>1022</v>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>R$ 800 – R$ 1.400</t>
+          <t>R$ 690 – R$ 1.400</t>
         </is>
       </c>
     </row>
@@ -732,27 +744,27 @@
         <v>3</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>R$ 180 – R$ 400</t>
+          <t>R$ 180 – R$ 350</t>
         </is>
       </c>
       <c r="G8" s="8" t="n">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>R$ 250 – R$ 600</t>
+          <t>R$ 250 – R$ 455</t>
         </is>
       </c>
       <c r="I8" s="10" t="n">
-        <v>496</v>
+        <v>457</v>
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>R$ 350 – R$ 800</t>
+          <t>R$ 216 – R$ 800</t>
         </is>
       </c>
     </row>
@@ -776,27 +788,27 @@
         <v>4</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>R$ 180 – R$ 400</t>
+          <t>R$ 180 – R$ 350</t>
         </is>
       </c>
       <c r="G9" s="8" t="n">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="H9" s="9" t="inlineStr">
         <is>
-          <t>R$ 228 – R$ 600</t>
+          <t>R$ 250 – R$ 455</t>
         </is>
       </c>
       <c r="I9" s="10" t="n">
-        <v>496</v>
+        <v>457</v>
       </c>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>R$ 350 – R$ 800</t>
+          <t>R$ 216 – R$ 800</t>
         </is>
       </c>
     </row>
@@ -820,27 +832,27 @@
         <v>4</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>R$ 180 – R$ 400</t>
+          <t>R$ 180 – R$ 350</t>
         </is>
       </c>
       <c r="G10" s="8" t="n">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>R$ 228 – R$ 600</t>
+          <t>R$ 250 – R$ 455</t>
         </is>
       </c>
       <c r="I10" s="10" t="n">
-        <v>496</v>
+        <v>457</v>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>R$ 350 – R$ 800</t>
+          <t>R$ 216 – R$ 800</t>
         </is>
       </c>
     </row>
@@ -864,27 +876,27 @@
         <v>5</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>R$ 200 – R$ 400</t>
+          <t>R$ 200 – R$ 390</t>
         </is>
       </c>
       <c r="G11" s="8" t="n">
-        <v>414</v>
+        <v>381</v>
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>R$ 260 – R$ 650</t>
+          <t>R$ 200 – R$ 504</t>
         </is>
       </c>
       <c r="I11" s="10" t="n">
-        <v>564</v>
+        <v>509</v>
       </c>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>R$ 350 – R$ 900</t>
+          <t>R$ 220 – R$ 900</t>
         </is>
       </c>
     </row>
@@ -908,27 +920,27 @@
         <v>5</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>R$ 200 – R$ 400</t>
+          <t>R$ 200 – R$ 390</t>
         </is>
       </c>
       <c r="G12" s="8" t="n">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="H12" s="9" t="inlineStr">
         <is>
-          <t>R$ 220 – R$ 650</t>
+          <t>R$ 200 – R$ 420</t>
         </is>
       </c>
       <c r="I12" s="10" t="n">
-        <v>564</v>
+        <v>509</v>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>R$ 350 – R$ 900</t>
+          <t>R$ 220 – R$ 900</t>
         </is>
       </c>
     </row>
@@ -952,27 +964,27 @@
         <v>5</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>R$ 200 – R$ 400</t>
+          <t>R$ 200 – R$ 390</t>
         </is>
       </c>
       <c r="G13" s="8" t="n">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="H13" s="9" t="inlineStr">
         <is>
-          <t>R$ 220 – R$ 650</t>
+          <t>R$ 200 – R$ 420</t>
         </is>
       </c>
       <c r="I13" s="10" t="n">
-        <v>564</v>
+        <v>509</v>
       </c>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>R$ 350 – R$ 900</t>
+          <t>R$ 220 – R$ 900</t>
         </is>
       </c>
     </row>
@@ -996,27 +1008,27 @@
         <v>8</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>R$ 400 – R$ 1.080</t>
+          <t>R$ 400 – R$ 715</t>
         </is>
       </c>
       <c r="G14" s="8" t="n">
-        <v>638</v>
+        <v>581</v>
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>R$ 400 – R$ 1.000</t>
+          <t>R$ 400 – R$ 715</t>
         </is>
       </c>
       <c r="I14" s="10" t="n">
-        <v>1034</v>
+        <v>904</v>
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>R$ 900 – R$ 1.400</t>
+          <t>R$ 600 – R$ 1.400</t>
         </is>
       </c>
     </row>
@@ -1040,27 +1052,27 @@
         <v>10</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>779</v>
+        <v>750</v>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>R$ 620 – R$ 1.320</t>
+          <t>R$ 620 – R$ 936</t>
         </is>
       </c>
       <c r="G15" s="8" t="n">
-        <v>997</v>
+        <v>921</v>
       </c>
       <c r="H15" s="9" t="inlineStr">
         <is>
+          <t>R$ 700 – R$ 1.200</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="n">
+        <v>1180</v>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
           <t>R$ 700 – R$ 1.500</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>R$ 780 – R$ 1.300</t>
         </is>
       </c>
     </row>
@@ -1084,27 +1096,27 @@
         <v>12</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>766</v>
+        <v>737</v>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>R$ 620 – R$ 1.200</t>
+          <t>R$ 620 – R$ 910</t>
         </is>
       </c>
       <c r="G16" s="8" t="n">
-        <v>997</v>
+        <v>921</v>
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
+          <t>R$ 700 – R$ 1.200</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="n">
+        <v>1177</v>
+      </c>
+      <c r="J16" s="11" t="inlineStr">
+        <is>
           <t>R$ 700 – R$ 1.500</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="n">
-        <v>1190</v>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
-          <t>R$ 780 – R$ 1.300</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1140,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
@@ -1136,19 +1148,19 @@
         </is>
       </c>
       <c r="G17" s="8" t="n">
-        <v>838</v>
+        <v>781</v>
       </c>
       <c r="H17" s="9" t="inlineStr">
         <is>
-          <t>R$ 494 – R$ 1.100</t>
+          <t>R$ 350 – R$ 920</t>
         </is>
       </c>
       <c r="I17" s="10" t="n">
-        <v>986</v>
+        <v>965</v>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>R$ 600 – R$ 1.200</t>
+          <t>R$ 588 – R$ 1.200</t>
         </is>
       </c>
     </row>
@@ -1232,13 +1244,13 @@
         <v>250</v>
       </c>
       <c r="E2" s="13" t="n">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="F2" s="13" t="n">
-        <v>600</v>
+        <v>494</v>
       </c>
       <c r="G2" s="12" t="n">
-        <v>227</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3">
@@ -1258,16 +1270,16 @@
         </is>
       </c>
       <c r="D3" s="15" t="n">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="E3" s="15" t="n">
-        <v>449</v>
+        <v>415</v>
       </c>
       <c r="F3" s="15" t="n">
-        <v>650</v>
+        <v>494</v>
       </c>
       <c r="G3" s="14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -1287,16 +1299,16 @@
         </is>
       </c>
       <c r="D4" s="17" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>795</v>
+        <v>613</v>
       </c>
       <c r="F4" s="17" t="n">
         <v>1000</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5">
@@ -1319,13 +1331,13 @@
         <v>200</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="F5" s="13" t="n">
         <v>494</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>262</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6">
@@ -1345,13 +1357,13 @@
         </is>
       </c>
       <c r="D6" s="15" t="n">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>425</v>
+        <v>407</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="G6" s="14" t="n">
         <v>42</v>
@@ -1374,16 +1386,16 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>490</v>
+        <v>250</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>702</v>
+        <v>584</v>
       </c>
       <c r="F7" s="17" t="n">
         <v>1100</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
@@ -1406,13 +1418,13 @@
         <v>400</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>518</v>
+        <v>492</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>1050</v>
+        <v>650</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>262</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9">
@@ -1432,10 +1444,10 @@
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>518</v>
+        <v>600</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>787</v>
+        <v>733</v>
       </c>
       <c r="F9" s="15" t="n">
         <v>1300</v>
@@ -1461,16 +1473,16 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>800</v>
+        <v>690</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>1165</v>
+        <v>1022</v>
       </c>
       <c r="F10" s="17" t="n">
         <v>1400</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -1493,13 +1505,13 @@
         <v>180</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>262</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12">
@@ -1522,10 +1534,10 @@
         <v>250</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>600</v>
+        <v>455</v>
       </c>
       <c r="G12" s="14" t="n">
         <v>42</v>
@@ -1548,16 +1560,16 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>350</v>
+        <v>216</v>
       </c>
       <c r="E13" s="17" t="n">
-        <v>496</v>
+        <v>457</v>
       </c>
       <c r="F13" s="17" t="n">
         <v>800</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -1580,13 +1592,13 @@
         <v>180</v>
       </c>
       <c r="E14" s="13" t="n">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="F14" s="13" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>262</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15">
@@ -1606,13 +1618,13 @@
         </is>
       </c>
       <c r="D15" s="15" t="n">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="F15" s="15" t="n">
-        <v>600</v>
+        <v>455</v>
       </c>
       <c r="G15" s="14" t="n">
         <v>42</v>
@@ -1635,16 +1647,16 @@
         </is>
       </c>
       <c r="D16" s="17" t="n">
-        <v>350</v>
+        <v>216</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>496</v>
+        <v>457</v>
       </c>
       <c r="F16" s="17" t="n">
         <v>800</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1667,13 +1679,13 @@
         <v>180</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>222</v>
+        <v>204</v>
       </c>
       <c r="F17" s="13" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>262</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18">
@@ -1693,13 +1705,13 @@
         </is>
       </c>
       <c r="D18" s="15" t="n">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="F18" s="15" t="n">
-        <v>600</v>
+        <v>455</v>
       </c>
       <c r="G18" s="14" t="n">
         <v>42</v>
@@ -1722,16 +1734,16 @@
         </is>
       </c>
       <c r="D19" s="17" t="n">
-        <v>350</v>
+        <v>216</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>496</v>
+        <v>457</v>
       </c>
       <c r="F19" s="17" t="n">
         <v>800</v>
       </c>
       <c r="G19" s="16" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -1754,13 +1766,13 @@
         <v>200</v>
       </c>
       <c r="E20" s="13" t="n">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>262</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21">
@@ -1780,13 +1792,13 @@
         </is>
       </c>
       <c r="D21" s="15" t="n">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>414</v>
+        <v>381</v>
       </c>
       <c r="F21" s="15" t="n">
-        <v>650</v>
+        <v>504</v>
       </c>
       <c r="G21" s="14" t="n">
         <v>42</v>
@@ -1809,16 +1821,16 @@
         </is>
       </c>
       <c r="D22" s="17" t="n">
-        <v>350</v>
+        <v>220</v>
       </c>
       <c r="E22" s="17" t="n">
-        <v>564</v>
+        <v>509</v>
       </c>
       <c r="F22" s="17" t="n">
         <v>900</v>
       </c>
       <c r="G22" s="16" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23">
@@ -1841,13 +1853,13 @@
         <v>200</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>262</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24">
@@ -1867,13 +1879,13 @@
         </is>
       </c>
       <c r="D24" s="15" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="F24" s="15" t="n">
-        <v>650</v>
+        <v>420</v>
       </c>
       <c r="G24" s="14" t="n">
         <v>42</v>
@@ -1896,16 +1908,16 @@
         </is>
       </c>
       <c r="D25" s="17" t="n">
-        <v>350</v>
+        <v>220</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>564</v>
+        <v>509</v>
       </c>
       <c r="F25" s="17" t="n">
         <v>900</v>
       </c>
       <c r="G25" s="16" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26">
@@ -1928,13 +1940,13 @@
         <v>200</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="F26" s="13" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>262</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27">
@@ -1954,13 +1966,13 @@
         </is>
       </c>
       <c r="D27" s="15" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="F27" s="15" t="n">
-        <v>650</v>
+        <v>420</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>42</v>
@@ -1983,16 +1995,16 @@
         </is>
       </c>
       <c r="D28" s="17" t="n">
-        <v>350</v>
+        <v>220</v>
       </c>
       <c r="E28" s="17" t="n">
-        <v>564</v>
+        <v>509</v>
       </c>
       <c r="F28" s="17" t="n">
         <v>900</v>
       </c>
       <c r="G28" s="16" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29">
@@ -2015,13 +2027,13 @@
         <v>400</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>1080</v>
+        <v>715</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30">
@@ -2044,10 +2056,10 @@
         <v>400</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>638</v>
+        <v>581</v>
       </c>
       <c r="F30" s="15" t="n">
-        <v>1000</v>
+        <v>715</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>42</v>
@@ -2070,16 +2082,16 @@
         </is>
       </c>
       <c r="D31" s="17" t="n">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="E31" s="17" t="n">
-        <v>1034</v>
+        <v>904</v>
       </c>
       <c r="F31" s="17" t="n">
         <v>1400</v>
       </c>
       <c r="G31" s="16" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32">
@@ -2102,13 +2114,13 @@
         <v>620</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>779</v>
+        <v>750</v>
       </c>
       <c r="F32" s="13" t="n">
-        <v>1320</v>
+        <v>936</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33">
@@ -2131,10 +2143,10 @@
         <v>700</v>
       </c>
       <c r="E33" s="15" t="n">
-        <v>997</v>
+        <v>921</v>
       </c>
       <c r="F33" s="15" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>42</v>
@@ -2157,16 +2169,16 @@
         </is>
       </c>
       <c r="D34" s="17" t="n">
-        <v>780</v>
+        <v>700</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>1190</v>
+        <v>1180</v>
       </c>
       <c r="F34" s="17" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="G34" s="16" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35">
@@ -2189,13 +2201,13 @@
         <v>620</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>766</v>
+        <v>737</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>1200</v>
+        <v>910</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="36">
@@ -2218,10 +2230,10 @@
         <v>700</v>
       </c>
       <c r="E36" s="15" t="n">
-        <v>997</v>
+        <v>921</v>
       </c>
       <c r="F36" s="15" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="G36" s="14" t="n">
         <v>42</v>
@@ -2244,16 +2256,16 @@
         </is>
       </c>
       <c r="D37" s="17" t="n">
-        <v>780</v>
+        <v>700</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>1190</v>
+        <v>1177</v>
       </c>
       <c r="F37" s="17" t="n">
-        <v>1300</v>
+        <v>1500</v>
       </c>
       <c r="G37" s="16" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38">
@@ -2276,13 +2288,13 @@
         <v>330</v>
       </c>
       <c r="E38" s="13" t="n">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F38" s="13" t="n">
         <v>910</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="39">
@@ -2302,16 +2314,16 @@
         </is>
       </c>
       <c r="D39" s="15" t="n">
-        <v>494</v>
+        <v>350</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>838</v>
+        <v>781</v>
       </c>
       <c r="F39" s="15" t="n">
-        <v>1100</v>
+        <v>920</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40">
@@ -2331,16 +2343,16 @@
         </is>
       </c>
       <c r="D40" s="17" t="n">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>986</v>
+        <v>965</v>
       </c>
       <c r="F40" s="17" t="n">
         <v>1200</v>
       </c>
       <c r="G40" s="16" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2355,7 +2367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2393,24 +2405,24 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>Alta temporada</t>
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Feriados</t>
         </is>
       </c>
       <c r="B2" s="18" t="n">
-        <v>46382</v>
+        <v>46305</v>
       </c>
       <c r="C2" s="18" t="n">
-        <v>46418</v>
-      </c>
-      <c r="D2" s="16" t="inlineStr">
-        <is>
-          <t>Réveillon + Janeiro</t>
-        </is>
-      </c>
-      <c r="E2" s="16" t="n">
-        <v>37</v>
+        <v>46308</v>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>Nossa Senhora Aparecida</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -2419,19 +2431,19 @@
           <t>Feriados</t>
         </is>
       </c>
-      <c r="B3" s="19" t="n">
-        <v>46305</v>
-      </c>
-      <c r="C3" s="19" t="n">
-        <v>46311</v>
+      <c r="B3" s="18" t="n">
+        <v>46326</v>
+      </c>
+      <c r="C3" s="18" t="n">
+        <v>46329</v>
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>N. Sra. Aparecida (12/out) + semana de pico</t>
+          <t>Finados</t>
         </is>
       </c>
       <c r="E3" s="14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2440,15 +2452,15 @@
           <t>Feriados</t>
         </is>
       </c>
-      <c r="B4" s="19" t="n">
-        <v>46326</v>
-      </c>
-      <c r="C4" s="19" t="n">
-        <v>46328</v>
+      <c r="B4" s="18" t="n">
+        <v>46340</v>
+      </c>
+      <c r="C4" s="18" t="n">
+        <v>46342</v>
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>Finados (02/nov)</t>
+          <t>Proclamação da República</t>
         </is>
       </c>
       <c r="E4" s="14" t="n">
@@ -2461,170 +2473,338 @@
           <t>Feriados</t>
         </is>
       </c>
-      <c r="B5" s="19" t="n">
-        <v>46346</v>
-      </c>
-      <c r="C5" s="19" t="n">
+      <c r="B5" s="18" t="n">
+        <v>46345</v>
+      </c>
+      <c r="C5" s="18" t="n">
         <v>46348</v>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Consciência Negra (20/nov)</t>
+          <t>Consciência Negra</t>
         </is>
       </c>
       <c r="E5" s="14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Alta temporada</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="n">
+        <v>46378</v>
+      </c>
+      <c r="C6" s="19" t="n">
+        <v>46382</v>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>Natal</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Alta temporada</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="n">
+        <v>46383</v>
+      </c>
+      <c r="C7" s="19" t="n">
+        <v>46384</v>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>Pré-Réveillon</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Alta temporada</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="n">
+        <v>46385</v>
+      </c>
+      <c r="C8" s="19" t="n">
+        <v>46387</v>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>Réveillon</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Alta temporada</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>46388</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>46390</v>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>Confraternização Universal</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Alta temporada</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>46391</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>46402</v>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>Verão Jan Início</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Alta temporada</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>46403</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>46410</v>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Verão Jan Meio</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Alta temporada</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>46411</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>46418</v>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>Verão Jan Fim</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Alta temporada</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>46423</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>46427</v>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>Carnaval</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>Feriados</t>
         </is>
       </c>
-      <c r="B6" s="19" t="n">
-        <v>46380</v>
-      </c>
-      <c r="C6" s="19" t="n">
-        <v>46381</v>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>Natal</t>
-        </is>
-      </c>
-      <c r="E6" s="14" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="B14" s="18" t="n">
+        <v>46428</v>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>46432</v>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>CarnaPorto</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Feriados</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
-        <v>46423</v>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>46430</v>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Carnaval + Carnaporto Axé Moi</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="B15" s="18" t="n">
+        <v>46471</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>46474</v>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>Páscoa</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Feriados</t>
         </is>
       </c>
-      <c r="B8" s="19" t="n">
-        <v>46468</v>
-      </c>
-      <c r="C8" s="19" t="n">
-        <v>46474</v>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>Semana Santa / Páscoa (28/mar)</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="n">
+      <c r="B16" s="18" t="n">
+        <v>46496</v>
+      </c>
+      <c r="C16" s="18" t="n">
+        <v>46502</v>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>Tiradentes</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Feriados</t>
         </is>
       </c>
-      <c r="B9" s="19" t="n">
-        <v>46498</v>
-      </c>
-      <c r="C9" s="19" t="n">
-        <v>46498</v>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>Tiradentes</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="B17" s="18" t="n">
+        <v>46507</v>
+      </c>
+      <c r="C17" s="18" t="n">
+        <v>46509</v>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Dia do Trabalho</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Feriados</t>
         </is>
       </c>
-      <c r="B10" s="19" t="n">
-        <v>46507</v>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>46509</v>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>Dia do Trabalho (01/mai)</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="n">
+      <c r="B18" s="18" t="n">
+        <v>46533</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>46537</v>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Corpus Christi</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Alta temporada</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="n">
+        <v>46575</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>46592</v>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>Férias escolares de Inverno</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Feriados</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="n">
+        <v>46636</v>
+      </c>
+      <c r="C20" s="18" t="n">
+        <v>46638</v>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Independência do Brasil</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Feriados</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="n">
-        <v>46534</v>
-      </c>
-      <c r="C11" s="19" t="n">
-        <v>46537</v>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>Corpus Christi (27/mai)</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>Feriados</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="n">
-        <v>46634</v>
-      </c>
-      <c r="C12" s="19" t="n">
-        <v>46637</v>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>Independência (07/set)</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Qualquer data fora desta lista = Tarifa Padrão.</t>
         </is>
